--- a/data/trans_dic/POLIPATOLOGIA_2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,04; 41,88</t>
+          <t>35,89; 41,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,56; 52,13</t>
+          <t>45,82; 52,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,85; 48,12</t>
+          <t>40,77; 48,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,52; 59,89</t>
+          <t>51,23; 59,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,72; 58,22</t>
+          <t>52,81; 58,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,78; 66,23</t>
+          <t>60,63; 66,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,21; 66,66</t>
+          <t>60,42; 66,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,82; 75,07</t>
+          <t>69,72; 74,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,99; 50,13</t>
+          <t>46,21; 50,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,2; 59,32</t>
+          <t>55,29; 59,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,89; 57,81</t>
+          <t>52,91; 57,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 67,98</t>
+          <t>63,27; 67,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 12,55</t>
+          <t>9,39; 12,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 17,19</t>
+          <t>13,79; 17,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 19,8</t>
+          <t>16,41; 19,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 29,62</t>
+          <t>17,79; 29,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 21,81</t>
+          <t>17,76; 21,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,57; 26,85</t>
+          <t>22,47; 26,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,79; 29,06</t>
+          <t>24,94; 28,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,09; 60,07</t>
+          <t>39,52; 61,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 16,45</t>
+          <t>13,96; 16,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 21,13</t>
+          <t>18,45; 21,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,95; 23,7</t>
+          <t>21,05; 23,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,44; 45,82</t>
+          <t>29,9; 44,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 14,22</t>
+          <t>8,59; 14,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,91</t>
+          <t>8,26; 14,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 21,79</t>
+          <t>15,02; 22,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,55; 30,57</t>
+          <t>23,63; 30,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,31</t>
+          <t>15,24; 22,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 24,24</t>
+          <t>16,48; 24,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,69</t>
+          <t>16,31; 23,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,98; 40,69</t>
+          <t>33,85; 40,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 17,04</t>
+          <t>12,51; 17,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 18,19</t>
+          <t>12,95; 17,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 21,59</t>
+          <t>16,69; 21,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 34,63</t>
+          <t>29,89; 34,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 21,02</t>
+          <t>18,45; 21,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 25,99</t>
+          <t>22,92; 25,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 25,34</t>
+          <t>22,46; 25,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,45; 33,43</t>
+          <t>23,27; 33,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,34</t>
+          <t>31,94; 35,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,14; 40,37</t>
+          <t>37,02; 40,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,59; 37,83</t>
+          <t>34,41; 38,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,09; 59,89</t>
+          <t>46,13; 59,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,53; 27,87</t>
+          <t>25,7; 27,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 32,83</t>
+          <t>30,53; 32,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 31,24</t>
+          <t>29,06; 31,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,31; 46,13</t>
+          <t>36,55; 45,75</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>371782; 432060</t>
+          <t>370294; 430870</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>444012; 508121</t>
+          <t>446583; 511922</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>308165; 362965</t>
+          <t>307574; 363759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265287; 308386</t>
+          <t>263820; 307666</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>693287; 765645</t>
+          <t>694486; 765954</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>813158; 886050</t>
+          <t>811170; 885068</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>598904; 663046</t>
+          <t>600990; 663776</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>527472; 567155</t>
+          <t>526718; 565446</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1079418; 1176506</t>
+          <t>1084399; 1179153</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1276419; 1371811</t>
+          <t>1278564; 1375492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>925109; 1011150</t>
+          <t>925324; 1010318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>803518; 863613</t>
+          <t>803828; 862241</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>160300; 212534</t>
+          <t>158955; 214108</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>270066; 337562</t>
+          <t>270809; 338594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>339502; 411085</t>
+          <t>340743; 411157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>415467; 678475</t>
+          <t>407372; 676699</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>284909; 346256</t>
+          <t>281980; 343759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>396766; 471962</t>
+          <t>395044; 474183</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>492820; 577707</t>
+          <t>495794; 574490</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>874840; 1344193</t>
+          <t>884296; 1383074</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>460382; 539897</t>
+          <t>458113; 541818</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>684848; 786434</t>
+          <t>686788; 791588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>851740; 963412</t>
+          <t>855752; 960085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1378459; 2074903</t>
+          <t>1353942; 2022510</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46862; 78384</t>
+          <t>47383; 80424</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40760; 71740</t>
+          <t>39730; 70454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79784; 119166</t>
+          <t>82151; 120646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152292; 197696</t>
+          <t>152793; 197762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73045; 106265</t>
+          <t>72617; 107652</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74019; 111193</t>
+          <t>75577; 110926</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92296; 130092</t>
+          <t>89560; 130461</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>224403; 268726</t>
+          <t>223579; 267182</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>127859; 175185</t>
+          <t>128618; 175967</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123990; 170930</t>
+          <t>121740; 168358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181096; 236631</t>
+          <t>182917; 234395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>388685; 452667</t>
+          <t>390703; 454860</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>602418; 688582</t>
+          <t>604686; 692536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>778256; 888866</t>
+          <t>783879; 882909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>755479; 855777</t>
+          <t>758655; 859414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>809446; 1154026</t>
+          <t>803418; 1148131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1079246; 1194125</t>
+          <t>1079368; 1189882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1320077; 1434937</t>
+          <t>1315643; 1437518</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1221856; 1336285</t>
+          <t>1215228; 1342904</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1684013; 2188101</t>
+          <t>1685329; 2156681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1699278; 1855089</t>
+          <t>1710286; 1847148</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2129203; 2289239</t>
+          <t>2128959; 2281911</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2000443; 2158337</t>
+          <t>2008174; 2158669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2580328; 3278130</t>
+          <t>2597369; 3250946</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,89; 41,76</t>
+          <t>36,08; 41,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,82; 52,52</t>
+          <t>45,91; 52,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,77; 48,22</t>
+          <t>40,49; 47,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,23; 59,75</t>
+          <t>48,83; 56,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,81; 58,24</t>
+          <t>52,72; 58,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,63; 66,16</t>
+          <t>60,91; 66,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,42; 66,73</t>
+          <t>60,57; 66,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,72; 74,84</t>
+          <t>69,08; 74,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,21; 50,24</t>
+          <t>46,12; 50,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,29; 59,48</t>
+          <t>55,13; 59,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,91; 57,77</t>
+          <t>52,71; 57,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,27; 67,87</t>
+          <t>61,47; 66,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,64</t>
+          <t>9,76; 12,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 17,24</t>
+          <t>13,88; 17,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 19,8</t>
+          <t>16,44; 19,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 29,55</t>
+          <t>26,43; 30,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 21,65</t>
+          <t>17,75; 21,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 26,98</t>
+          <t>22,79; 26,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 28,89</t>
+          <t>24,86; 29,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,52; 61,8</t>
+          <t>37,47; 41,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 16,51</t>
+          <t>13,94; 16,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,27</t>
+          <t>18,56; 21,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,62</t>
+          <t>21,02; 23,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 44,67</t>
+          <t>32,5; 35,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,59</t>
+          <t>8,58; 14,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,64</t>
+          <t>8,37; 14,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 22,06</t>
+          <t>14,88; 22,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 30,58</t>
+          <t>23,75; 30,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,24; 22,6</t>
+          <t>14,75; 22,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 24,19</t>
+          <t>16,52; 23,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 23,76</t>
+          <t>16,51; 23,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 40,45</t>
+          <t>34,23; 40,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 17,12</t>
+          <t>12,48; 17,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,91</t>
+          <t>13,11; 17,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,39</t>
+          <t>16,48; 21,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,89; 34,8</t>
+          <t>30,3; 35,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,14</t>
+          <t>18,38; 21,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 25,82</t>
+          <t>22,7; 25,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 25,44</t>
+          <t>22,53; 25,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,26</t>
+          <t>30,47; 33,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,21</t>
+          <t>31,92; 35,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,02; 40,45</t>
+          <t>37,08; 40,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,41; 38,02</t>
+          <t>34,44; 37,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,13; 59,03</t>
+          <t>44,76; 47,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,7; 27,75</t>
+          <t>25,72; 27,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 32,72</t>
+          <t>30,49; 32,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,06; 31,24</t>
+          <t>29,02; 31,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 45,75</t>
+          <t>38,24; 40,51</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287549</t>
+          <t>305653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>546991</t>
+          <t>590605</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>834541</t>
+          <t>896258</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>370294; 430870</t>
+          <t>372214; 432871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>446583; 511922</t>
+          <t>447483; 508518</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>307574; 363759</t>
+          <t>305462; 359831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263820; 307666</t>
+          <t>282519; 329509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>694486; 765954</t>
+          <t>693388; 763504</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>811170; 885068</t>
+          <t>814821; 883076</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>600990; 663776</t>
+          <t>602467; 661897</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>526718; 565446</t>
+          <t>567871; 610586</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1084399; 1179153</t>
+          <t>1082427; 1178353</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1278564; 1375492</t>
+          <t>1274868; 1373447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>925324; 1010318</t>
+          <t>921901; 1006813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>803828; 862241</t>
+          <t>860973; 927801</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588020</t>
+          <t>633466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1035067</t>
+          <t>854181</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1623087</t>
+          <t>1487647</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>158955; 214108</t>
+          <t>165263; 214895</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>270809; 338594</t>
+          <t>272575; 335260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>340743; 411157</t>
+          <t>341362; 412747</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>407372; 676699</t>
+          <t>589525; 678858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>281980; 343759</t>
+          <t>281886; 348365</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>395044; 474183</t>
+          <t>400653; 473051</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>495794; 574490</t>
+          <t>494226; 579372</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>884296; 1383074</t>
+          <t>813518; 893028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>458113; 541818</t>
+          <t>457524; 541485</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>686788; 791588</t>
+          <t>690848; 790947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>855752; 960085</t>
+          <t>854559; 965439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1353942; 2022510</t>
+          <t>1430736; 1556291</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174945</t>
+          <t>196570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>246082</t>
+          <t>274848</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>421027</t>
+          <t>471418</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47383; 80424</t>
+          <t>47295; 77629</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39730; 70454</t>
+          <t>40289; 71460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82151; 120646</t>
+          <t>81394; 120369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152793; 197762</t>
+          <t>169012; 218936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72617; 107652</t>
+          <t>70279; 107070</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75577; 110926</t>
+          <t>75753; 109855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89560; 130461</t>
+          <t>90680; 130542</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>223579; 267182</t>
+          <t>251512; 295836</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>128618; 175967</t>
+          <t>128242; 176349</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121740; 168358</t>
+          <t>123210; 168807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182917; 234395</t>
+          <t>180633; 239189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>390703; 454860</t>
+          <t>438251; 508910</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1050515</t>
+          <t>1135689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1828140</t>
+          <t>1719633</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2878655</t>
+          <t>2855322</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>604686; 692536</t>
+          <t>602391; 693201</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>783879; 882909</t>
+          <t>776197; 884381</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>758655; 859414</t>
+          <t>761084; 860485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>803418; 1148131</t>
+          <t>1072769; 1190210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1079368; 1189882</t>
+          <t>1078673; 1189146</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1315643; 1437518</t>
+          <t>1317777; 1431580</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1215228; 1342904</t>
+          <t>1216286; 1335416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1685329; 2156681</t>
+          <t>1668737; 1774342</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1710286; 1847148</t>
+          <t>1711947; 1860969</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2128959; 2281911</t>
+          <t>2126459; 2285886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2008174; 2158669</t>
+          <t>2005432; 2158878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2597369; 3250946</t>
+          <t>2772301; 2936634</t>
         </is>
       </c>
     </row>
